--- a/Testing_outputs.xlsx
+++ b/Testing_outputs.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Python_Projects\PLS-R\rPET Eval June 2025\reheat data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel Turmer\Documents\placement_stuff\raman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CB6845-2177-4125-A9E5-5CC0C7CFE7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CBBD03-1402-492D-83E2-4049C964E24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-1680" windowWidth="38640" windowHeight="21120" xr2:uid="{89376997-067B-48A0-8D8A-FF71CDE45DB9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{89376997-067B-48A0-8D8A-FF71CDE45DB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,23 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Mix_A</t>
-  </si>
-  <si>
-    <t>Mix_B</t>
-  </si>
-  <si>
-    <t>Mix_C</t>
-  </si>
-  <si>
-    <t>Mix_D</t>
-  </si>
-  <si>
-    <t>Mix_E</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,27 +414,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A51D79AD-6D40-4DB8-8086-C5EB1DD270AD}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:E2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>96.582930000000005</v>
       </c>
